--- a/insumos/03_enlistamiento/00_piloto/Base Prueba Piloto EnighurAC.XLSX
+++ b/insumos/03_enlistamiento/00_piloto/Base Prueba Piloto EnighurAC.XLSX
@@ -4997,10 +4997,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5310,7 +5311,7 @@
     <col min="20" max="20" width="5.6640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="26.109375" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="33.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="7.5546875" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="58.33203125" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="33.88671875" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="5.5546875" bestFit="1" customWidth="1"/>
@@ -6035,94 +6036,105 @@
       </c>
     </row>
     <row r="8" spans="1:41" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+      <c r="A8" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="N8" s="1" t="s">
+      <c r="N8" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="O8" s="1" t="s">
+      <c r="O8" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="P8" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="R8" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="W8" s="1" t="s">
+      <c r="Q8" s="2"/>
+      <c r="R8" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="V8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="W8" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="X8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AD8" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="AE8" s="1" t="s">
+      <c r="X8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Y8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z8" s="2"/>
+      <c r="AA8" s="2"/>
+      <c r="AB8" s="2"/>
+      <c r="AC8" s="2"/>
+      <c r="AD8" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AE8" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="AF8" s="1" t="s">
+      <c r="AF8" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="AG8" s="1" t="s">
+      <c r="AG8" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AH8" s="1" t="s">
+      <c r="AH8" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="AI8" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="AJ8" s="1" t="s">
+      <c r="AI8" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="AL8" s="1" t="s">
+      <c r="AK8" s="2"/>
+      <c r="AL8" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="AM8" s="1" t="s">
+      <c r="AM8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="AN8" s="1" t="s">
+      <c r="AN8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="AO8" s="1"/>
+      <c r="AO8" s="3"/>
     </row>
     <row r="9" spans="1:41" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
